--- a/eval_output/資材課_尤秐棠_評分表.xlsx
+++ b/eval_output/資材課_尤秐棠_評分表.xlsx
@@ -1332,6 +1332,11 @@
           <t>劉祐誠</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>鍾欣芳</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">

--- a/eval_output/資材課_尤秐棠_評分表.xlsx
+++ b/eval_output/資材課_尤秐棠_評分表.xlsx
@@ -1279,60 +1279,35 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>白惇維</t>
+          <t>王柳琦</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>王柳琦</t>
+          <t>徐惠蘭</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>徐惠蘭</t>
+          <t>沙洋</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>沙洋</t>
+          <t>周清家</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>朱冠瑋</t>
+          <t>詹郁瑛</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>周清家</t>
+          <t>林依婷</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
-        <is>
-          <t>詹郁瑛</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>林依婷</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>曾夷璋</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>陳家祥</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>劉祐誠</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
         <is>
           <t>鍾欣芳</t>
         </is>

--- a/eval_output/資材課_尤秐棠_評分表.xlsx
+++ b/eval_output/資材課_尤秐棠_評分表.xlsx
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,6 +268,9 @@
       <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -346,6 +349,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -796,7 +803,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:M6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -897,14 +904,20 @@
       <c r="E8" s="14" t="n"/>
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="14" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
     </row>
     <row r="9" ht="39.5" customHeight="1">
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>【行政】工作項目是否能在工時內完成?</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">✓準時上下班工作均能完成 (9-10)
 ✓偶爾加班也能完成工作 (7-8)
@@ -919,18 +932,30 @@
       <c r="E9" s="14" t="n"/>
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="14" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="15" t="n"/>
     </row>
     <row r="10" ht="42.5" customHeight="1">
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>*低於等於2分或高於等於8分，請說明原因：_________________________</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="15" t="n"/>
     </row>
     <row r="11" ht="113.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -938,12 +963,12 @@
           <t>團隊溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>受評者的溝通協調與配合度</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>✓非常願意溝通協調且配合度極高 (16-20)
 ✓願意溝通協調且配合度高 (12-15)
@@ -952,20 +977,26 @@
 ✓非常不願意溝通協調且配合度極低 (0-3)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="n"/>
+      <c r="D11" s="21" t="n"/>
       <c r="E11" s="14" t="n"/>
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="14" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="15" t="n"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="11" t="n"/>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">你對於受評者在會議追蹤事項之執行、回覆與結案管理上，是否能依規定期限完成並有效追蹤事項進度之表現評價為何？
 </t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>10分：會議追蹤事項皆能準時完成並主動追蹤，結案完整無需提醒
 7~9分：大多能準時完成，偶有延遲但能主動回覆並完成結案
@@ -977,6 +1008,12 @@
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="14" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="n"/>
     </row>
     <row r="13" ht="49.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -984,7 +1021,7 @@
           <t>工作表現30%</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
@@ -993,14 +1030,20 @@
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="14" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="15" t="n"/>
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="15" t="n"/>
     </row>
     <row r="14" ht="49.5" customHeight="1">
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>你對於受評者完成工作之品質與完整性評價為何？</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>10分：工作完整且品質穩定，可直接使用
 7~9分：大致完整，少量修正即可
@@ -1012,9 +1055,15 @@
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="14" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
@@ -1023,14 +1072,20 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15" t="n"/>
+      <c r="L15" s="15" t="n"/>
+      <c r="M15" s="15" t="n"/>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>你對於受評者在工作目標、交辦事項及時程管理上的達成能力評價為何？</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>10分：能有效規劃並穩定達成目標
 7~9分：大多能如期完成
@@ -1042,9 +1097,15 @@
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
@@ -1053,15 +1114,21 @@
       <c r="E17" s="14" t="n"/>
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="11" t="n"/>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>對於主管交辦事項，受評者是否能正確理解需求、依規範執行並有效完成？</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>10分：能主動確認需求並高品質完成
 7~9分：大多能獨立完成
@@ -1073,14 +1140,20 @@
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="14" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
     </row>
     <row r="19" ht="49" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>工作態度30%</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>*低於等於2分或高於等於9分，請說明原因： _________________________</t>
         </is>
@@ -1089,14 +1162,20 @@
       <c r="E19" s="14" t="n"/>
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="14" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
     </row>
     <row r="20" ht="32.5" customHeight="1">
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>是否願意和受評者一起工作?</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>我很願意跟受評者一起工作(15~20)
 我還算願意跟受評者一起工作(8~14)
@@ -1108,39 +1187,75 @@
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
     </row>
     <row r="21" ht="28.5" customHeight="1">
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>*低於等於3分或最高分，請敘述狀況：_________________________</t>
         </is>
       </c>
-      <c r="D21" s="30" t="n"/>
+      <c r="D21" s="31" t="n"/>
       <c r="E21" s="14" t="n"/>
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
     </row>
     <row r="22" ht="50.5" customHeight="1">
-      <c r="B22" s="31" t="n"/>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <f>SUM(D8:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <f>SUM(E8:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <f>SUM(F8:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <f>SUM(G8:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>SUM(H8:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="34">
+        <f>SUM(I8:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="34">
+        <f>SUM(J8:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="34">
+        <f>SUM(K8:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="34">
+        <f>SUM(L8:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="34">
+        <f>SUM(M8:M21)</f>
         <v/>
       </c>
     </row>
@@ -1185,8 +1300,69 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="H23" s="7">
+        <f>IF(OR(
+  AND(H22&gt;=90, COUNTIF($D$22:$Z$22, "&gt;=90")/COUNTA($D$22:$Z$22)&gt;0.05),
+  AND(H22&gt;=80,H22&lt;=89, (COUNTIF($D$22:$Z$22, "&gt;=80")-COUNTIF($D$22:$Z$22, "&gt;=90"))/COUNTA($D$22:$Z$22)&gt;0.2),
+  AND(H22&gt;=70,H22&lt;=79, (COUNTIF($D$22:$Z$22, "&gt;=70")-COUNTIF($D$22:$Z$22, "&gt;=80"))/COUNTA($D$22:$Z$22)&gt;0.4),
+  AND(H22&gt;=60,H22&lt;=69, (COUNTIF($D$22:$Z$22, "&gt;=60")-COUNTIF($D$22:$Z$22, "&gt;=70"))/COUNTA($D$22:$Z$22)&gt;0.3),
+  AND(H22&lt;=59, COUNTIF($D$22:$Z$22, "&lt;=59")/COUNTA($D$22:$Z$22)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="I23" s="7">
+        <f>IF(OR(
+  AND(I22&gt;=90, COUNTIF($D$22:$Z$22, "&gt;=90")/COUNTA($D$22:$Z$22)&gt;0.05),
+  AND(I22&gt;=80,I22&lt;=89, (COUNTIF($D$22:$Z$22, "&gt;=80")-COUNTIF($D$22:$Z$22, "&gt;=90"))/COUNTA($D$22:$Z$22)&gt;0.2),
+  AND(I22&gt;=70,I22&lt;=79, (COUNTIF($D$22:$Z$22, "&gt;=70")-COUNTIF($D$22:$Z$22, "&gt;=80"))/COUNTA($D$22:$Z$22)&gt;0.4),
+  AND(I22&gt;=60,I22&lt;=69, (COUNTIF($D$22:$Z$22, "&gt;=60")-COUNTIF($D$22:$Z$22, "&gt;=70"))/COUNTA($D$22:$Z$22)&gt;0.3),
+  AND(I22&lt;=59, COUNTIF($D$22:$Z$22, "&lt;=59")/COUNTA($D$22:$Z$22)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="J23" s="7">
+        <f>IF(OR(
+  AND(J22&gt;=90, COUNTIF($D$22:$Z$22, "&gt;=90")/COUNTA($D$22:$Z$22)&gt;0.05),
+  AND(J22&gt;=80,J22&lt;=89, (COUNTIF($D$22:$Z$22, "&gt;=80")-COUNTIF($D$22:$Z$22, "&gt;=90"))/COUNTA($D$22:$Z$22)&gt;0.2),
+  AND(J22&gt;=70,J22&lt;=79, (COUNTIF($D$22:$Z$22, "&gt;=70")-COUNTIF($D$22:$Z$22, "&gt;=80"))/COUNTA($D$22:$Z$22)&gt;0.4),
+  AND(J22&gt;=60,J22&lt;=69, (COUNTIF($D$22:$Z$22, "&gt;=60")-COUNTIF($D$22:$Z$22, "&gt;=70"))/COUNTA($D$22:$Z$22)&gt;0.3),
+  AND(J22&lt;=59, COUNTIF($D$22:$Z$22, "&lt;=59")/COUNTA($D$22:$Z$22)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="K23" s="7">
+        <f>IF(OR(
+  AND(K22&gt;=90, COUNTIF($D$22:$Z$22, "&gt;=90")/COUNTA($D$22:$Z$22)&gt;0.05),
+  AND(K22&gt;=80,K22&lt;=89, (COUNTIF($D$22:$Z$22, "&gt;=80")-COUNTIF($D$22:$Z$22, "&gt;=90"))/COUNTA($D$22:$Z$22)&gt;0.2),
+  AND(K22&gt;=70,K22&lt;=79, (COUNTIF($D$22:$Z$22, "&gt;=70")-COUNTIF($D$22:$Z$22, "&gt;=80"))/COUNTA($D$22:$Z$22)&gt;0.4),
+  AND(K22&gt;=60,K22&lt;=69, (COUNTIF($D$22:$Z$22, "&gt;=60")-COUNTIF($D$22:$Z$22, "&gt;=70"))/COUNTA($D$22:$Z$22)&gt;0.3),
+  AND(K22&lt;=59, COUNTIF($D$22:$Z$22, "&lt;=59")/COUNTA($D$22:$Z$22)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="L23" s="7">
+        <f>IF(OR(
+  AND(L22&gt;=90, COUNTIF($D$22:$Z$22, "&gt;=90")/COUNTA($D$22:$Z$22)&gt;0.05),
+  AND(L22&gt;=80,L22&lt;=89, (COUNTIF($D$22:$Z$22, "&gt;=80")-COUNTIF($D$22:$Z$22, "&gt;=90"))/COUNTA($D$22:$Z$22)&gt;0.2),
+  AND(L22&gt;=70,L22&lt;=79, (COUNTIF($D$22:$Z$22, "&gt;=70")-COUNTIF($D$22:$Z$22, "&gt;=80"))/COUNTA($D$22:$Z$22)&gt;0.4),
+  AND(L22&gt;=60,L22&lt;=69, (COUNTIF($D$22:$Z$22, "&gt;=60")-COUNTIF($D$22:$Z$22, "&gt;=70"))/COUNTA($D$22:$Z$22)&gt;0.3),
+  AND(L22&lt;=59, COUNTIF($D$22:$Z$22, "&lt;=59")/COUNTA($D$22:$Z$22)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="M23" s="7">
+        <f>IF(OR(
+  AND(M22&gt;=90, COUNTIF($D$22:$Z$22, "&gt;=90")/COUNTA($D$22:$Z$22)&gt;0.05),
+  AND(M22&gt;=80,M22&lt;=89, (COUNTIF($D$22:$Z$22, "&gt;=80")-COUNTIF($D$22:$Z$22, "&gt;=90"))/COUNTA($D$22:$Z$22)&gt;0.2),
+  AND(M22&gt;=70,M22&lt;=79, (COUNTIF($D$22:$Z$22, "&gt;=70")-COUNTIF($D$22:$Z$22, "&gt;=80"))/COUNTA($D$22:$Z$22)&gt;0.4),
+  AND(M22&gt;=60,M22&lt;=69, (COUNTIF($D$22:$Z$22, "&gt;=60")-COUNTIF($D$22:$Z$22, "&gt;=70"))/COUNTA($D$22:$Z$22)&gt;0.3),
+  AND(M22&lt;=59, COUNTIF($D$22:$Z$22, "&lt;=59")/COUNTA($D$22:$Z$22)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="12">
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="A2:I2"/>
@@ -1222,14 +1398,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>樂聯工業股份有限公司</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>2025年度 年終 績效考核跨部門共同評分表(非主管職)</t>
         </is>
@@ -1265,7 +1441,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:J6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1314,24 +1490,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>占比</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>題目</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>評分方式</t>
         </is>
       </c>
     </row>
     <row r="8" ht="33.5" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>工作知識20%</t>
         </is>
@@ -1346,19 +1522,26 @@
           <t>根據考核固定成績</t>
         </is>
       </c>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9" ht="123" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>跨部門溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>跨部門協辦時，交代是否清楚？（15 分）</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>✓任務交代內容完整（目的、時程、資料、條件）；對方能一次理解；無需再次確認；無誤會或重工。 (13-15)
 ✓大部分交代清楚；偶有細節不足但不影響進度。 (10-12)
@@ -1367,16 +1550,22 @@
 ✓未交代清楚或資訊錯誤；造成流程延誤、返工或責任互推。 (0-3)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="37" t="n"/>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="A10" s="38" t="n"/>
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>是否透過正確窗口、不越權、不跳層級？（15 分）</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>✓所有跨部門需求皆走正確窗口；不直接跳主管下指令；不跨部門亂交辦；資訊一致且透明。 (13-15)
 ✓大部分遵守窗口；偶有直接聯繫但不造成誤會。 (10-12)
@@ -1385,29 +1574,41 @@
 ✓反覆越權、直接指揮他人或跳主管；造成部門衝突或重大錯誤。 (0-3)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>跨部門工作表現30%</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>*低於等於6分或高於13分，請說明原因：____________________</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">跨部門回覆速度與協作度（15 分）
 </t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>✓回覆迅速（一般案件 30–60 分鐘內）；主動更新進度；積極協作、不推託。 (13-15)
 ✓回覆通常在當天，偶有延遲但會說明。 (10-12)
@@ -1416,26 +1617,38 @@
 ✓長期不回覆或拒絕協作；造成重大流程中斷。 (0-3)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13" ht="44.5" customHeight="1">
-      <c r="A13" s="42" t="n"/>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="A13" s="44" t="n"/>
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>*低於等於6分或高於13分，請說明原因：____________________</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="37" t="n"/>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="A14" s="38" t="n"/>
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>遇到問題時，是否會先查制度流程？（15 分）</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">✓遇到問題會先查 SOP、流程、辦法，再提出問題；提問前已掌握背景資訊；80% 以上問題能自行依制度解決 (13-15)
 ✓大部分情況會查制度；偶爾先問人，但提問內容完整。 (10-12)
@@ -1445,29 +1658,41 @@
 </t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15" ht="62.5" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>跨部門工作態度
 35%</t>
         </is>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>*低於等於6分或高於等於13分，請說明原因：_________________________</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16" ht="62.5" customHeight="1">
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>資料正確性與完整性（20 分）</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>✓資料一次到位、完整正確；無需補件；不造成延誤；正確率 95% 以上。(16-20)
 ✓偶有小錯但能立即補齊；不影響流程；正確率 85–94% (13-15)
@@ -1476,27 +1701,63 @@
 ✓錯誤頻繁；資料重大缺漏；造成流程中斷或退件；正確率 &lt;50%。 (0-3)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>*低於等於8分或高於等於16分，請說明原因： _________________________</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18" ht="23.5" customHeight="1">
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="50">
         <f>SUM(D8:D17)</f>
         <v/>
       </c>
-      <c r="AK18" s="49" t="n"/>
+      <c r="E18" s="50">
+        <f>SUM(E8:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="50">
+        <f>SUM(F8:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="50">
+        <f>SUM(G8:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="50">
+        <f>SUM(H8:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="50">
+        <f>SUM(I8:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="50">
+        <f>SUM(J8:J17)</f>
+        <v/>
+      </c>
+      <c r="AK18" s="51" t="n"/>
     </row>
     <row r="19">
       <c r="D19" s="7">
@@ -1509,8 +1770,69 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="E19" s="7">
+        <f>IF(OR(
+  AND(E18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(E18&gt;=80,E18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(E18&gt;=70,E18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(E18&gt;=60,E18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(E18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="F19" s="7">
+        <f>IF(OR(
+  AND(F18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(F18&gt;=80,F18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(F18&gt;=70,F18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(F18&gt;=60,F18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(F18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="G19" s="7">
+        <f>IF(OR(
+  AND(G18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(G18&gt;=80,G18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(G18&gt;=70,G18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(G18&gt;=60,G18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(G18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="H19" s="7">
+        <f>IF(OR(
+  AND(H18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(H18&gt;=80,H18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(H18&gt;=70,H18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(H18&gt;=60,H18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(H18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="I19" s="7">
+        <f>IF(OR(
+  AND(I18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(I18&gt;=80,I18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(I18&gt;=70,I18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(I18&gt;=60,I18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(I18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="J19" s="7">
+        <f>IF(OR(
+  AND(J18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(J18&gt;=80,J18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(J18&gt;=70,J18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(J18&gt;=60,J18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(J18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="9">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C12:C13"/>
